--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P333"/>
+  <dimension ref="A1:P334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18436,6 +18436,60 @@
         <v>341.04</v>
       </c>
       <c r="P333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>290.94</v>
+      </c>
+      <c r="C334" t="n">
+        <v>298.88</v>
+      </c>
+      <c r="D334" t="n">
+        <v>309.17</v>
+      </c>
+      <c r="E334" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="F334" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="G334" t="n">
+        <v>322.67</v>
+      </c>
+      <c r="H334" t="n">
+        <v>323.83</v>
+      </c>
+      <c r="I334" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="J334" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="K334" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="L334" t="n">
+        <v>339.33</v>
+      </c>
+      <c r="M334" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="N334" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="O334" t="n">
+        <v>340.23</v>
+      </c>
+      <c r="P334" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18452,7 +18506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B343"/>
+  <dimension ref="A1:B344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21885,6 +21939,16 @@
       </c>
       <c r="B343" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -22053,28 +22117,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2703808814621445</v>
+        <v>0.2643147489611768</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05059404092096909</v>
+        <v>0.04859239915003644</v>
       </c>
       <c r="M2" t="n">
-        <v>6.958760248027577</v>
+        <v>6.964455854681975</v>
       </c>
       <c r="N2" t="n">
-        <v>74.22873331378894</v>
+        <v>74.29713191655264</v>
       </c>
       <c r="O2" t="n">
-        <v>8.615609863137312</v>
+        <v>8.619578407123671</v>
       </c>
       <c r="P2" t="n">
-        <v>293.5995040725124</v>
+        <v>293.6648970948957</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22135,28 +22199,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3358476152874177</v>
+        <v>0.3287535962692279</v>
       </c>
       <c r="J3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08629032934201097</v>
+        <v>0.08303403161095568</v>
       </c>
       <c r="M3" t="n">
-        <v>6.309316441457483</v>
+        <v>6.323659793841742</v>
       </c>
       <c r="N3" t="n">
-        <v>64.62464011256411</v>
+        <v>64.82896622065552</v>
       </c>
       <c r="O3" t="n">
-        <v>8.038945211441867</v>
+        <v>8.051643696827096</v>
       </c>
       <c r="P3" t="n">
-        <v>301.461554612525</v>
+        <v>301.5380282708847</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22217,28 +22281,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3326091986476284</v>
+        <v>0.3252699313034828</v>
       </c>
       <c r="J4" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09932244414816194</v>
+        <v>0.09531394030247986</v>
       </c>
       <c r="M4" t="n">
-        <v>5.957459028515529</v>
+        <v>5.972656655427669</v>
       </c>
       <c r="N4" t="n">
-        <v>54.28226476887217</v>
+        <v>54.54567108366719</v>
       </c>
       <c r="O4" t="n">
-        <v>7.367649880991372</v>
+        <v>7.385504118451712</v>
       </c>
       <c r="P4" t="n">
-        <v>312.2412454754765</v>
+        <v>312.3203629153998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22299,28 +22363,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3662401022223533</v>
+        <v>0.3616524481022266</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1374796667054204</v>
+        <v>0.1348874046588178</v>
       </c>
       <c r="M5" t="n">
-        <v>5.510785356797533</v>
+        <v>5.515734765275073</v>
       </c>
       <c r="N5" t="n">
-        <v>45.5334093189505</v>
+        <v>45.56328560261151</v>
       </c>
       <c r="O5" t="n">
-        <v>6.747844790668388</v>
+        <v>6.750058192535196</v>
       </c>
       <c r="P5" t="n">
-        <v>319.0303954955859</v>
+        <v>319.0798504932332</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22381,28 +22445,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3225778574358493</v>
+        <v>0.3185750146686372</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1133877819990157</v>
+        <v>0.1112916399700233</v>
       </c>
       <c r="M6" t="n">
-        <v>5.493762382017795</v>
+        <v>5.4959445373725</v>
       </c>
       <c r="N6" t="n">
-        <v>44.02547623998623</v>
+        <v>44.02011023892929</v>
       </c>
       <c r="O6" t="n">
-        <v>6.635169646662113</v>
+        <v>6.634765273838201</v>
       </c>
       <c r="P6" t="n">
-        <v>319.580324423254</v>
+        <v>319.6234751435245</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22463,28 +22527,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2474206688971908</v>
+        <v>0.2433124736517323</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K7" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08138358960261971</v>
+        <v>0.07915221393086624</v>
       </c>
       <c r="M7" t="n">
-        <v>4.912356600877001</v>
+        <v>4.91687248552698</v>
       </c>
       <c r="N7" t="n">
-        <v>37.38839447919256</v>
+        <v>37.40972436781765</v>
       </c>
       <c r="O7" t="n">
-        <v>6.114605014160158</v>
+        <v>6.116348940979222</v>
       </c>
       <c r="P7" t="n">
-        <v>322.754821029734</v>
+        <v>322.7991074517003</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22545,28 +22609,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2329462515712417</v>
+        <v>0.2278873925699311</v>
       </c>
       <c r="J8" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K8" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07574870242839382</v>
+        <v>0.07281080745576629</v>
       </c>
       <c r="M8" t="n">
-        <v>4.820825118406927</v>
+        <v>4.830238846667865</v>
       </c>
       <c r="N8" t="n">
-        <v>35.82562938876898</v>
+        <v>35.9206420735125</v>
       </c>
       <c r="O8" t="n">
-        <v>5.985451477438355</v>
+        <v>5.993383190945869</v>
       </c>
       <c r="P8" t="n">
-        <v>325.8483722769349</v>
+        <v>325.9029068720585</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22627,28 +22691,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2838982935520221</v>
+        <v>0.279269580405841</v>
       </c>
       <c r="J9" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K9" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.116834565323983</v>
+        <v>0.1136548726820948</v>
       </c>
       <c r="M9" t="n">
-        <v>4.654938693035377</v>
+        <v>4.662459711430133</v>
       </c>
       <c r="N9" t="n">
-        <v>32.96581257745165</v>
+        <v>33.03642508010125</v>
       </c>
       <c r="O9" t="n">
-        <v>5.741586242272396</v>
+        <v>5.74773216843837</v>
       </c>
       <c r="P9" t="n">
-        <v>333.5507863972529</v>
+        <v>333.6006840119729</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22709,28 +22773,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3145464351551306</v>
+        <v>0.3077138699413572</v>
       </c>
       <c r="J10" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K10" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1248763197811883</v>
+        <v>0.119838727948001</v>
       </c>
       <c r="M10" t="n">
-        <v>4.880613361982941</v>
+        <v>4.90555134909001</v>
       </c>
       <c r="N10" t="n">
-        <v>37.51685151883935</v>
+        <v>37.77375749987551</v>
       </c>
       <c r="O10" t="n">
-        <v>6.125100123168546</v>
+        <v>6.14603591755495</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8243730489477</v>
+        <v>330.8980282303813</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22791,28 +22855,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.266696137108118</v>
+        <v>0.2616929034885722</v>
       </c>
       <c r="J11" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K11" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1003488530862248</v>
+        <v>0.09707660825623987</v>
       </c>
       <c r="M11" t="n">
-        <v>4.606454101654837</v>
+        <v>4.618675689572809</v>
       </c>
       <c r="N11" t="n">
-        <v>34.503462541611</v>
+        <v>34.59801482222018</v>
       </c>
       <c r="O11" t="n">
-        <v>5.87396480595611</v>
+        <v>5.88200772034687</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4142883043974</v>
+        <v>336.4682232568599</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22873,28 +22937,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2278778022271206</v>
+        <v>0.222548571780481</v>
       </c>
       <c r="J12" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K12" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07807877129271634</v>
+        <v>0.07474366978058866</v>
       </c>
       <c r="M12" t="n">
-        <v>4.648292854489101</v>
+        <v>4.662670674841404</v>
       </c>
       <c r="N12" t="n">
-        <v>33.17663955168577</v>
+        <v>33.30184152431772</v>
       </c>
       <c r="O12" t="n">
-        <v>5.759916627147113</v>
+        <v>5.77077477677978</v>
       </c>
       <c r="P12" t="n">
-        <v>341.9231791056912</v>
+        <v>341.9806283100775</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22955,28 +23019,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.208101947020411</v>
+        <v>0.2039922424894438</v>
       </c>
       <c r="J13" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K13" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05612766598897001</v>
+        <v>0.05422749337979993</v>
       </c>
       <c r="M13" t="n">
-        <v>5.035497017473053</v>
+        <v>5.041467250003713</v>
       </c>
       <c r="N13" t="n">
-        <v>39.4054295105546</v>
+        <v>39.4208004253814</v>
       </c>
       <c r="O13" t="n">
-        <v>6.277374412169039</v>
+        <v>6.27859860362019</v>
       </c>
       <c r="P13" t="n">
-        <v>352.6006582455914</v>
+        <v>352.6449609376837</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -23037,28 +23101,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08972553660008084</v>
+        <v>0.08571115595285288</v>
       </c>
       <c r="J14" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K14" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01004804899054779</v>
+        <v>0.009212287927038765</v>
       </c>
       <c r="M14" t="n">
-        <v>5.287838975516117</v>
+        <v>5.293360993420294</v>
       </c>
       <c r="N14" t="n">
-        <v>42.91726180599906</v>
+        <v>42.91595605795043</v>
       </c>
       <c r="O14" t="n">
-        <v>6.551126758504911</v>
+        <v>6.551027099466955</v>
       </c>
       <c r="P14" t="n">
-        <v>346.5924958383839</v>
+        <v>346.6357709372178</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -23119,28 +23183,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1626633573990748</v>
+        <v>0.1572736760246771</v>
       </c>
       <c r="J15" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K15" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02681628352397403</v>
+        <v>0.0251715792546291</v>
       </c>
       <c r="M15" t="n">
-        <v>5.890245985287407</v>
+        <v>5.902517813659652</v>
       </c>
       <c r="N15" t="n">
-        <v>51.95689792003899</v>
+        <v>52.03083230108695</v>
       </c>
       <c r="O15" t="n">
-        <v>7.208113339844137</v>
+        <v>7.213240069558683</v>
       </c>
       <c r="P15" t="n">
-        <v>344.6702927718118</v>
+        <v>344.7283936383356</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -23182,7 +23246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P333"/>
+  <dimension ref="A1:P334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50491,6 +50555,88 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-35.440540392116006,174.41414551867337</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-35.44027801783022,174.41498791388204</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-35.43999144744761,174.4158397111638</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-35.43964078593411,174.41669082933203</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-35.43929116875352,174.4175243765623</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-35.43892683652336,174.418322216995</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-35.43853131396046,174.41909118628507</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-35.438061233316105,174.41982560667532</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-35.437589163625745,174.42055697873764</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-35.43703086275593,174.4211665766211</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-35.43645476428143,174.42174480845307</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-35.43581785642546,174.4222449005461</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-35.435160061793525,174.42269794955294</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-35.43448892644432,174.42306068148903</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P334"/>
+  <dimension ref="A1:P336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18490,6 +18490,114 @@
         <v>340.23</v>
       </c>
       <c r="P334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>292.12</v>
+      </c>
+      <c r="C335" t="n">
+        <v>299.87</v>
+      </c>
+      <c r="D335" t="n">
+        <v>310.78</v>
+      </c>
+      <c r="E335" t="n">
+        <v>323.18</v>
+      </c>
+      <c r="F335" t="n">
+        <v>323.27</v>
+      </c>
+      <c r="G335" t="n">
+        <v>324.58</v>
+      </c>
+      <c r="H335" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="I335" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="J335" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="K335" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="L335" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="M335" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="N335" t="n">
+        <v>342.42</v>
+      </c>
+      <c r="O335" t="n">
+        <v>342.01</v>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>291.99</v>
+      </c>
+      <c r="C336" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="D336" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="E336" t="n">
+        <v>323.32</v>
+      </c>
+      <c r="F336" t="n">
+        <v>323.52</v>
+      </c>
+      <c r="G336" t="n">
+        <v>325.18</v>
+      </c>
+      <c r="H336" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="I336" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="J336" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="K336" t="n">
+        <v>337.62</v>
+      </c>
+      <c r="L336" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="M336" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="N336" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="O336" t="n">
+        <v>342.52</v>
+      </c>
+      <c r="P336" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18506,7 +18614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B344"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21949,6 +22057,26 @@
       </c>
       <c r="B344" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -22117,28 +22245,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2643147489611768</v>
+        <v>0.2537777977541943</v>
       </c>
       <c r="J2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04859239915003644</v>
+        <v>0.04529404953632976</v>
       </c>
       <c r="M2" t="n">
-        <v>6.964455854681975</v>
+        <v>6.969219114026864</v>
       </c>
       <c r="N2" t="n">
-        <v>74.29713191655264</v>
+        <v>74.29732491935208</v>
       </c>
       <c r="O2" t="n">
-        <v>8.619578407123671</v>
+        <v>8.619589602721934</v>
       </c>
       <c r="P2" t="n">
-        <v>293.6648970948957</v>
+        <v>293.7788406183108</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22199,28 +22327,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3287535962692279</v>
+        <v>0.316376749628263</v>
       </c>
       <c r="J3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08303403161095568</v>
+        <v>0.07767026770228314</v>
       </c>
       <c r="M3" t="n">
-        <v>6.323659793841742</v>
+        <v>6.343339926267449</v>
       </c>
       <c r="N3" t="n">
-        <v>64.82896622065552</v>
+        <v>65.05459485242655</v>
       </c>
       <c r="O3" t="n">
-        <v>8.051643696827096</v>
+        <v>8.065642866655239</v>
       </c>
       <c r="P3" t="n">
-        <v>301.5380282708847</v>
+        <v>301.6718658727375</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22281,28 +22409,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3252699313034828</v>
+        <v>0.313323028951836</v>
       </c>
       <c r="J4" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09531394030247986</v>
+        <v>0.08930619773917259</v>
       </c>
       <c r="M4" t="n">
-        <v>5.972656655427669</v>
+        <v>5.99070967291009</v>
       </c>
       <c r="N4" t="n">
-        <v>54.54567108366719</v>
+        <v>54.79145886816268</v>
       </c>
       <c r="O4" t="n">
-        <v>7.385504118451712</v>
+        <v>7.40212529400595</v>
       </c>
       <c r="P4" t="n">
-        <v>312.3203629153998</v>
+        <v>312.449550422634</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22363,28 +22491,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3616524481022266</v>
+        <v>0.3549459154482238</v>
       </c>
       <c r="J5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1348874046588178</v>
+        <v>0.1316765153389339</v>
       </c>
       <c r="M5" t="n">
-        <v>5.515734765275073</v>
+        <v>5.513825776942063</v>
       </c>
       <c r="N5" t="n">
-        <v>45.56328560261151</v>
+        <v>45.47105575179508</v>
       </c>
       <c r="O5" t="n">
-        <v>6.750058192535196</v>
+        <v>6.743222949880501</v>
       </c>
       <c r="P5" t="n">
-        <v>319.0798504932332</v>
+        <v>319.1523723345911</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22445,28 +22573,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3185750146686372</v>
+        <v>0.3127928858501407</v>
       </c>
       <c r="J6" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K6" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1112916399700233</v>
+        <v>0.1087379023128299</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4959445373725</v>
+        <v>5.489968042459312</v>
       </c>
       <c r="N6" t="n">
-        <v>44.02011023892929</v>
+        <v>43.89101972010305</v>
       </c>
       <c r="O6" t="n">
-        <v>6.634765273838201</v>
+        <v>6.62502979012948</v>
       </c>
       <c r="P6" t="n">
-        <v>319.6234751435245</v>
+        <v>319.686000455841</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22527,28 +22655,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2433124736517323</v>
+        <v>0.2379271903888799</v>
       </c>
       <c r="J7" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K7" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07915221393086624</v>
+        <v>0.0766888188165058</v>
       </c>
       <c r="M7" t="n">
-        <v>4.91687248552698</v>
+        <v>4.91295103406575</v>
       </c>
       <c r="N7" t="n">
-        <v>37.40972436781765</v>
+        <v>37.30281860548804</v>
       </c>
       <c r="O7" t="n">
-        <v>6.116348940979222</v>
+        <v>6.107603343823831</v>
       </c>
       <c r="P7" t="n">
-        <v>322.7991074517003</v>
+        <v>322.8573404014437</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22609,28 +22737,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2278873925699311</v>
+        <v>0.2211961485514499</v>
       </c>
       <c r="J8" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K8" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07281080745576629</v>
+        <v>0.06943899245216933</v>
       </c>
       <c r="M8" t="n">
-        <v>4.830238846667865</v>
+        <v>4.832813336008395</v>
       </c>
       <c r="N8" t="n">
-        <v>35.9206420735125</v>
+        <v>35.88674027430097</v>
       </c>
       <c r="O8" t="n">
-        <v>5.993383190945869</v>
+        <v>5.990554254349172</v>
       </c>
       <c r="P8" t="n">
-        <v>325.9029068720585</v>
+        <v>325.9752607503371</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22691,28 +22819,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.279269580405841</v>
+        <v>0.2721147237124883</v>
       </c>
       <c r="J9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1136548726820948</v>
+        <v>0.109243585608621</v>
       </c>
       <c r="M9" t="n">
-        <v>4.662459711430133</v>
+        <v>4.6676570499249</v>
       </c>
       <c r="N9" t="n">
-        <v>33.03642508010125</v>
+        <v>33.0449078394979</v>
       </c>
       <c r="O9" t="n">
-        <v>5.74773216843837</v>
+        <v>5.748470043367878</v>
       </c>
       <c r="P9" t="n">
-        <v>333.6006840119729</v>
+        <v>333.6780517548875</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22773,28 +22901,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3077138699413572</v>
+        <v>0.2965835112382475</v>
       </c>
       <c r="J10" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K10" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.119838727948001</v>
+        <v>0.1123290171745697</v>
       </c>
       <c r="M10" t="n">
-        <v>4.90555134909001</v>
+        <v>4.940660467840656</v>
       </c>
       <c r="N10" t="n">
-        <v>37.77375749987551</v>
+        <v>38.04446832792939</v>
       </c>
       <c r="O10" t="n">
-        <v>6.14603591755495</v>
+        <v>6.168019806058456</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8980282303813</v>
+        <v>331.0183857786236</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22855,28 +22983,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2616929034885722</v>
+        <v>0.2539552999945604</v>
       </c>
       <c r="J11" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K11" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09707660825623987</v>
+        <v>0.09249507923983558</v>
       </c>
       <c r="M11" t="n">
-        <v>4.618675689572809</v>
+        <v>4.631495830411353</v>
       </c>
       <c r="N11" t="n">
-        <v>34.59801482222018</v>
+        <v>34.63238266386205</v>
       </c>
       <c r="O11" t="n">
-        <v>5.88200772034687</v>
+        <v>5.884928433197981</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4682232568599</v>
+        <v>336.5518920950834</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22937,28 +23065,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.222548571780481</v>
+        <v>0.2134850814020846</v>
       </c>
       <c r="J12" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K12" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07474366978058866</v>
+        <v>0.06943087378645629</v>
       </c>
       <c r="M12" t="n">
-        <v>4.662670674841404</v>
+        <v>4.68306116164083</v>
       </c>
       <c r="N12" t="n">
-        <v>33.30184152431772</v>
+        <v>33.43247445994471</v>
       </c>
       <c r="O12" t="n">
-        <v>5.77077477677978</v>
+        <v>5.782082190694344</v>
       </c>
       <c r="P12" t="n">
-        <v>341.9806283100775</v>
+        <v>342.0786353753049</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -23019,28 +23147,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2039922424894438</v>
+        <v>0.1976508467681045</v>
       </c>
       <c r="J13" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K13" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05422749337979993</v>
+        <v>0.05153986655883414</v>
       </c>
       <c r="M13" t="n">
-        <v>5.041467250003713</v>
+        <v>5.044167942037121</v>
       </c>
       <c r="N13" t="n">
-        <v>39.4208004253814</v>
+        <v>39.34690706945698</v>
       </c>
       <c r="O13" t="n">
-        <v>6.27859860362019</v>
+        <v>6.27271130130002</v>
       </c>
       <c r="P13" t="n">
-        <v>352.6449609376837</v>
+        <v>352.7135326596389</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -23101,28 +23229,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08571115595285288</v>
+        <v>0.07825679949251475</v>
       </c>
       <c r="J14" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K14" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009212287927038765</v>
+        <v>0.00775566454905563</v>
       </c>
       <c r="M14" t="n">
-        <v>5.293360993420294</v>
+        <v>5.301243481084307</v>
       </c>
       <c r="N14" t="n">
-        <v>42.91595605795043</v>
+        <v>42.88261158434818</v>
       </c>
       <c r="O14" t="n">
-        <v>6.551027099466955</v>
+        <v>6.548481624342255</v>
       </c>
       <c r="P14" t="n">
-        <v>346.6357709372178</v>
+        <v>346.7163777849178</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -23183,28 +23311,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1572736760246771</v>
+        <v>0.1491865502742153</v>
       </c>
       <c r="J15" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K15" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0251715792546291</v>
+        <v>0.02289729359568071</v>
       </c>
       <c r="M15" t="n">
-        <v>5.902517813659652</v>
+        <v>5.912110060821173</v>
       </c>
       <c r="N15" t="n">
-        <v>52.03083230108695</v>
+        <v>51.98198463463795</v>
       </c>
       <c r="O15" t="n">
-        <v>7.213240069558683</v>
+        <v>7.209853301880555</v>
       </c>
       <c r="P15" t="n">
-        <v>344.7283936383356</v>
+        <v>344.8158436664687</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -23246,7 +23374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P334"/>
+  <dimension ref="A1:P336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50637,6 +50765,170 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-35.44053016086075,174.4141419601041</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-35.44026943399532,174.41498492825673</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-35.43997760961729,174.41583436068757</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-35.43962565375254,174.41668279980905</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-35.43927856338135,174.4175160385876</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-35.43891201706951,174.41831150422985</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-35.438514962481996,174.41907867667038</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-35.43805300238805,174.41981790470433</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-35.43757966152687,174.42054601021965</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-35.437023445283415,174.42115710660227</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-35.43645063699473,174.4217389756229</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-35.435812887394626,174.4222349272237</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-35.435160129351075,174.42269815380504</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-35.43448300737516,174.42304245742784</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-35.44053128803295,174.41414235214984</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-35.44026483860891,174.41498332989192</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-35.439970733676645,174.41583170206655</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-35.43962449609929,174.4166821855287</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-35.43927658140452,174.41751472758554</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-35.43890736174347,174.41830813896416</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-35.438507015968575,174.4190725972333</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-35.43804684708497,174.41981214497056</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-35.43757415686221,174.42053965604487</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-35.43701696278578,174.42114883028472</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-35.43644550736655,174.42173172624908</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-35.43580960595868,174.42222834106806</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-35.43515773105777,174.42269090285646</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-35.434481311461546,174.42303723592764</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
